--- a/data/trans_bre/IP19C08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Estudios-trans_bre.xlsx
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 6,86</t>
+          <t>-10,3; 7,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,96; -1,4</t>
+          <t>-12,01; -1,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,12 +675,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 0,0</t>
+          <t>-13,57; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-86,13; 245,55</t>
+          <t>-85,58; 296,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 3,56</t>
+          <t>-3,19; 3,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,64</t>
+          <t>-1,58; 4,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 4,44</t>
+          <t>-1,31; 4,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 2,18</t>
+          <t>-5,16; 2,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,16; 109,64</t>
+          <t>-49,84; 93,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,99; 190,27</t>
+          <t>-32,8; 189,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,09; 213,3</t>
+          <t>-32,61; 201,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-87,17; 238,09</t>
+          <t>-88,28; 217,89</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 11,41</t>
+          <t>0,24; 11,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 5,89</t>
+          <t>-4,75; 4,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 3,3</t>
+          <t>-2,61; 3,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 1,63</t>
+          <t>-6,68; 1,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,43; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-78,58; 478,95</t>
+          <t>-82,18; 385,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-85,04; 78,1</t>
+          <t>-87,32; 118,23</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,63</t>
+          <t>-1,69; 3,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,87</t>
+          <t>-1,85; 2,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,49</t>
+          <t>-0,93; 3,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,86</t>
+          <t>-4,22; 0,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 112,01</t>
+          <t>-29,28; 108,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,37; 104,03</t>
+          <t>-40,03; 101,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 224,81</t>
+          <t>-26,32; 211,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-78,35; 48,89</t>
+          <t>-76,9; 55,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Estudios-trans_bre.xlsx
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 7,69</t>
+          <t>-11,93; 7,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,01; -1,37</t>
+          <t>-12,59; -1,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,12 +675,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 0,0</t>
+          <t>-16,18; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-85,58; 296,63</t>
+          <t>-94,66; 254,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 3,19</t>
+          <t>-3,26; 3,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 4,55</t>
+          <t>-1,15; 4,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,19</t>
+          <t>-1,37; 4,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 2,04</t>
+          <t>-4,74; 1,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,84; 93,94</t>
+          <t>-50,14; 109,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,8; 189,42</t>
+          <t>-28,36; 192,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,61; 201,48</t>
+          <t>-32,08; 202,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,28; 217,89</t>
+          <t>-87,59; 168,06</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 11,74</t>
+          <t>0,3; 11,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 4,91</t>
+          <t>-4,7; 4,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 3,32</t>
+          <t>-3,29; 3,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 1,83</t>
+          <t>-6,92; 1,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>-53,73; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-85,67; 387,68</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-82,18; 385,42</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-87,32; 118,23</t>
+          <t>-88,84; 81,6</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 3,8</t>
+          <t>-1,93; 3,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,7</t>
+          <t>-1,98; 2,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,36</t>
+          <t>-1,13; 3,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,92</t>
+          <t>-4,34; 0,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 108,92</t>
+          <t>-32,14; 98,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 101,22</t>
+          <t>-39,02; 110,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 211,14</t>
+          <t>-31,49; 190,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-76,9; 55,14</t>
+          <t>-74,56; 49,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,45</t>
+          <t>-4,06</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 7,01</t>
+          <t>-11,6; 6,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,59; -1,41</t>
+          <t>-11,96; -1,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,12 +675,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 0,0</t>
+          <t>-15,14; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-94,66; 254,36</t>
+          <t>-86,13; 245,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,47</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-13,37%</t>
+          <t>-16,96%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 3,5</t>
+          <t>-3,01; 3,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,9</t>
+          <t>-1,53; 4,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 4,43</t>
+          <t>-1,43; 4,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 1,92</t>
+          <t>-5,5; 2,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,14; 109,39</t>
+          <t>-45,16; 109,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 192,39</t>
+          <t>-35,99; 190,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,08; 202,49</t>
+          <t>-35,09; 213,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-87,59; 168,06</t>
+          <t>-88,58; 226,2</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,25</t>
+          <t>-2,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-46,78%</t>
+          <t>-48,8%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 11,27</t>
+          <t>0,1; 11,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 4,98</t>
+          <t>-4,29; 5,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 3,39</t>
+          <t>-3,34; 3,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 1,55</t>
+          <t>-6,58; 1,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,73; —</t>
+          <t>-54,43; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-85,67; 387,68</t>
+          <t>-78,58; 478,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-88,84; 81,6</t>
+          <t>-86,53; 72,65</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-34,5%</t>
+          <t>-35,39%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,47</t>
+          <t>-1,57; 3,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 2,68</t>
+          <t>-2,2; 2,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,23</t>
+          <t>-0,98; 3,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,9</t>
+          <t>-4,98; 0,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 98,14</t>
+          <t>-27,65; 112,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,02; 110,87</t>
+          <t>-43,37; 104,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 190,32</t>
+          <t>-29,56; 224,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,56; 49,21</t>
+          <t>-80,66; 46,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,181 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,67</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-4,47</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,06</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-20,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.673260472398234</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-4.467062588565602</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-4.060456924995758</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.2044565055260995</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-11,6; 6,86</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-11,96; -1,4</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-15,14; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-86,13; 245,55</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-11.59787633331572</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-11.95565939821333</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>-15.13577017308238</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.86125107087145</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.863275873447028</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-1.401314398360448</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.455507339596464</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,47</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>39,44%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>44,77%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-16,96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,01; 3,56</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,53; 4,64</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,43; 4,44</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-5,5; 2,15</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-45,16; 109,64</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-35,99; 190,27</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-35,09; 213,3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-88,58; 226,2</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.06808518554342335</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.466518988061213</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.476207660114043</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.4727898928897408</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.01327769000514845</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.394418147156909</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.4477303992370402</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1696181510893258</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4,9</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,52</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,27</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>262,7%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,98%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-48,8%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.009336065530775</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.530849702521072</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.43105768056516</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-5.504313207291398</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4516214086907236</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.359918258618824</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.350884337525145</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.8857592624925302</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 11,41</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,29; 5,89</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,34; 3,3</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-6,58; 1,47</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-54,43; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-78,58; 478,95</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-86,53; 72,65</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.559398812125457</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.644728484179186</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.440376569146062</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.147707653061493</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.096366726717074</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.902736495197822</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>2.133039132746703</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>2.261961671859843</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +801,191 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,19</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>44,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-35,39%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>4.896678865372679</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5218845468159108</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.3899502742171854</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-2.268849338893194</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>2.626983091193208</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.1471108459847646</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.239755391985722</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.4880482839183227</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; 3,63</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,2; 2,87</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,98; 3,49</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,98; 0,83</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-27,65; 112,01</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-43,37; 104,03</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-29,56; 224,81</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-80,66; 46,59</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.09787629020638264</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.289396515137382</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.338031877019539</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.582280906330555</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5442579003538068</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.785754963413843</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="n">
+        <v>-0.8652516608232381</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>11.40873541379056</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.893967685432191</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.296565359832351</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.473402297753568</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="n">
+        <v>4.789542860743611</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="n">
+        <v>0.7264525314576639</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8787124413446652</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4448692499210684</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.169473112872999</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.192126196924952</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1819113149722423</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1180711723481298</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.4420876906362824</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.3539366863001872</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.574532706912602</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.204999073967761</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.97955425636728</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.983185191467434</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2764832455049856</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4337334115989743</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2956085855526211</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.8066301299534092</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.627750789319445</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.871438786975572</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.489782038389122</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.8330199795247242</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.120076726868758</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.040336738483317</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.248101233475155</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.465908947781777</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +993,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
